--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.406661284165514</v>
+        <v>1.203582458676896</v>
       </c>
       <c r="D2" t="n">
-        <v>21.98037249464402</v>
+        <v>3.571810530379653</v>
       </c>
       <c r="E2" t="n">
-        <v>21.75526556150468</v>
+        <v>3.53523065374451</v>
       </c>
       <c r="F2" t="n">
-        <v>20.55167957426639</v>
+        <v>3.339647930818288</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.91719240717487</v>
+        <v>8.274043766165915</v>
       </c>
       <c r="D3" t="n">
-        <v>63.0837316431768</v>
+        <v>10.25110639201623</v>
       </c>
       <c r="E3" t="n">
-        <v>21.75526556150468</v>
+        <v>3.53523065374451</v>
       </c>
       <c r="F3" t="n">
-        <v>20.55167957426639</v>
+        <v>3.339647930818288</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
